--- a/data/trans_orig/P71_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P71_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2007</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2007 (tasa de respuesta: 98,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82254</t>
+          <t>82842</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119554</t>
+          <t>119751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>141302</t>
+          <t>142535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>185180</t>
+          <t>185126</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>235665</t>
+          <t>233075</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>293305</t>
+          <t>290758</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>566046</t>
+          <t>565849</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>603346</t>
+          <t>602758</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>493743</t>
+          <t>493797</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>537621</t>
+          <t>536388</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1071218</t>
+          <t>1073765</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1128858</t>
+          <t>1131448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>133681</t>
+          <t>136600</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>184658</t>
+          <t>183634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>221627</t>
+          <t>222076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>278399</t>
+          <t>281405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>372989</t>
+          <t>372894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>446237</t>
+          <t>443565</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>762772</t>
+          <t>763796</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>813749</t>
+          <t>810830</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>671860</t>
+          <t>668854</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>728632</t>
+          <t>728183</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1451452</t>
+          <t>1454124</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1524700</t>
+          <t>1524795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111459</t>
+          <t>110641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154110</t>
+          <t>154283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>184003</t>
+          <t>182234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>227763</t>
+          <t>227707</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>306037</t>
+          <t>306722</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>369671</t>
+          <t>371239</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517552</t>
+          <t>517379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>560203</t>
+          <t>561021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441225</t>
+          <t>441281</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>484985</t>
+          <t>486754</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>970979</t>
+          <t>969411</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1034613</t>
+          <t>1033928</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,12%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171054</t>
+          <t>170691</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>219673</t>
+          <t>220441</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>276746</t>
+          <t>273669</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>334698</t>
+          <t>333019</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>461047</t>
+          <t>461321</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>535285</t>
+          <t>533936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>706464</t>
+          <t>705696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>755083</t>
+          <t>755446</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>682101</t>
+          <t>683780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>740053</t>
+          <t>743130</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1407650</t>
+          <t>1408999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1481888</t>
+          <t>1481614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>536405</t>
+          <t>542936</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>626782</t>
+          <t>627470</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>873035</t>
+          <t>873730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>977713</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1429935</t>
+          <t>1443179</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1569869</t>
+          <t>1577379</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2604047</t>
+          <t>2603359</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2694424</t>
+          <t>2687893</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2337256</t>
+          <t>2336996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2441934</t>
+          <t>2441239</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4975929</t>
+          <t>4968419</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5115863</t>
+          <t>5102619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2012</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2012 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>173694</t>
+          <t>176615</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>221503</t>
+          <t>223530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>187893</t>
+          <t>186372</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>237718</t>
+          <t>236414</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>374434</t>
+          <t>373794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>445749</t>
+          <t>443614</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>478869</t>
+          <t>476842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>526678</t>
+          <t>523757</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>454314</t>
+          <t>455618</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>504139</t>
+          <t>505660</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>946655</t>
+          <t>948790</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1017970</t>
+          <t>1018610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,15%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>325752</t>
+          <t>328435</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>390558</t>
+          <t>390370</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>331956</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>396865</t>
+          <t>394949</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>678832</t>
+          <t>682816</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>773812</t>
+          <t>770833</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,84%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>622988</t>
+          <t>623176</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>687794</t>
+          <t>685111</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>626918</t>
+          <t>628834</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>690007</t>
+          <t>691827</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1263516</t>
+          <t>1266495</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1358496</t>
+          <t>1354512</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>239912</t>
+          <t>240680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>293904</t>
+          <t>295341</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>257157</t>
+          <t>259068</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>314151</t>
+          <t>311437</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>513563</t>
+          <t>510449</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>589780</t>
+          <t>588563</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>459810</t>
+          <t>458373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513802</t>
+          <t>513034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>460855</t>
+          <t>463569</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>517849</t>
+          <t>515938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>938940</t>
+          <t>940157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1015157</t>
+          <t>1018271</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,61%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>192222</t>
+          <t>194837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>246612</t>
+          <t>246274</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>231078</t>
+          <t>232744</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>289587</t>
+          <t>288747</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>443013</t>
+          <t>442873</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>518506</t>
+          <t>520004</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>694902</t>
+          <t>695240</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>749292</t>
+          <t>746677</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>762314</t>
+          <t>763154</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>820823</t>
+          <t>819157</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1474909</t>
+          <t>1473411</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1550402</t>
+          <t>1550542</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>992066</t>
+          <t>988394</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1098336</t>
+          <t>1099963</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,82 +4067,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>32,27%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1119928</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1059267</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1179250</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>31,61%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>29,9%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>33,29%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2163863</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2087027</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2239782</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>31,13%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>30,02%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>32,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1119928</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1061306</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1178750</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>31,61%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>29,96%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>33,27%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2163863</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>2081858</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2243353</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>31,13%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>29,95%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2310809</t>
+          <t>2309182</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2417079</t>
+          <t>2420751</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,82 +4180,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>67,73%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>71,01%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2253</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2422794</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2363472</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2483455</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>68,39%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>66,71%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>70,1%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>4468</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>4788004</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>4712085</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4864840</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>68,87%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>67,78%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>70,9%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2253</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2422794</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2363972</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2481416</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>68,39%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>66,73%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>70,04%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>4468</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>4788004</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>4708514</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4870009</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>68,87%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>67,73%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,98%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2016</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2016 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>205667</t>
+          <t>206811</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>254169</t>
+          <t>258133</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>208444</t>
+          <t>206678</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>254652</t>
+          <t>255170</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>425477</t>
+          <t>429017</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>496354</t>
+          <t>499943</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411162</t>
+          <t>407198</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>459664</t>
+          <t>458520</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>410260</t>
+          <t>409742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>456468</t>
+          <t>458234</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>833889</t>
+          <t>830300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>904766</t>
+          <t>901226</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,75%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>314360</t>
+          <t>313925</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>377033</t>
+          <t>378984</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>334175</t>
+          <t>330549</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>394881</t>
+          <t>392066</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>666165</t>
+          <t>663199</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>755539</t>
+          <t>750105</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>637490</t>
+          <t>635539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>700163</t>
+          <t>700598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>640270</t>
+          <t>643085</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>700976</t>
+          <t>704602</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1294134</t>
+          <t>1299568</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1383508</t>
+          <t>1386474</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,64%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>291498</t>
+          <t>290974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>347702</t>
+          <t>348060</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>337374</t>
+          <t>336772</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>393864</t>
+          <t>393484</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>644321</t>
+          <t>643005</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>722575</t>
+          <t>729322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,39%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>407336</t>
+          <t>406978</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>463540</t>
+          <t>464064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>390083</t>
+          <t>390463</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>446573</t>
+          <t>447175</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>816410</t>
+          <t>809663</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>894664</t>
+          <t>895980</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,22%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>205802</t>
+          <t>208081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>259304</t>
+          <t>261068</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>270968</t>
+          <t>270746</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>331735</t>
+          <t>331726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>493399</t>
+          <t>492717</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>575037</t>
+          <t>569818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>673086</t>
+          <t>671322</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>726588</t>
+          <t>724309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>711048</t>
+          <t>711057</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>771815</t>
+          <t>772037</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1400136</t>
+          <t>1405355</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1481774</t>
+          <t>1482456</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,05%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1075363</t>
+          <t>1069847</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1183427</t>
+          <t>1184093</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1203999</t>
+          <t>1198004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1316227</t>
+          <t>1315886</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2308918</t>
+          <t>2314822</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2472259</t>
+          <t>2470344</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2183855</t>
+          <t>2183189</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2291919</t>
+          <t>2297435</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2210565</t>
+          <t>2210906</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2322793</t>
+          <t>2328788</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4421816</t>
+          <t>4423731</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4585157</t>
+          <t>4579253</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,42%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2023</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2023 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56983</t>
+          <t>58071</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90064</t>
+          <t>90163</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86160</t>
+          <t>84682</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125011</t>
+          <t>127233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154839</t>
+          <t>155323</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>206454</t>
+          <t>206250</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>527281</t>
+          <t>527182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>560362</t>
+          <t>559274</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>588079</t>
+          <t>585857</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>626930</t>
+          <t>628408</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1123980</t>
+          <t>1124184</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1175595</t>
+          <t>1175111</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60927</t>
+          <t>49142</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148984</t>
+          <t>146534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>115366</t>
+          <t>115969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>153560</t>
+          <t>153218</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>165551</t>
+          <t>163393</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>288033</t>
+          <t>289754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1032424</t>
+          <t>1034874</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1120481</t>
+          <t>1132266</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>797247</t>
+          <t>797589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>835441</t>
+          <t>834838</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1844182</t>
+          <t>1842461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1966664</t>
+          <t>1968822</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76978</t>
+          <t>76375</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120629</t>
+          <t>117753</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54440</t>
+          <t>58466</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160229</t>
+          <t>161549</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131733</t>
+          <t>125974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>255846</t>
+          <t>256120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>579297</t>
+          <t>582173</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622948</t>
+          <t>623551</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>735634</t>
+          <t>734314</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>841423</t>
+          <t>837397</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1339943</t>
+          <t>1339669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1464056</t>
+          <t>1469815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115586</t>
+          <t>111344</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163256</t>
+          <t>158649</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>181973</t>
+          <t>182900</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>410541</t>
+          <t>425367</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>316363</t>
+          <t>316729</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>567746</t>
+          <t>589047</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>753969</t>
+          <t>758576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>801639</t>
+          <t>805881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>673420</t>
+          <t>658594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>901988</t>
+          <t>901061</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1433441</t>
+          <t>1412140</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1684824</t>
+          <t>1684458</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>329674</t>
+          <t>317457</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>465813</t>
+          <t>466090</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>518264</t>
+          <t>504971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>809900</t>
+          <t>788405</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>904865</t>
+          <t>894116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1231268</t>
+          <t>1219741</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2950090</t>
+          <t>2949813</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3086229</t>
+          <t>3098446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2833822</t>
+          <t>2855317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3125458</t>
+          <t>3138751</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5828357</t>
+          <t>5839884</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6154760</t>
+          <t>6165509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P71_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P71_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82842</t>
+          <t>82849</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119751</t>
+          <t>119381</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>142535</t>
+          <t>140470</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>185126</t>
+          <t>186009</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>233075</t>
+          <t>235617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>290758</t>
+          <t>292206</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>565849</t>
+          <t>566219</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>602758</t>
+          <t>602751</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>493797</t>
+          <t>492914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>536388</t>
+          <t>538453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1073765</t>
+          <t>1072317</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1131448</t>
+          <t>1128906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,73%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>136600</t>
+          <t>135501</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>183634</t>
+          <t>182970</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>222076</t>
+          <t>224029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>281405</t>
+          <t>280007</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>372894</t>
+          <t>371266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>443565</t>
+          <t>445143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>763796</t>
+          <t>764460</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>810830</t>
+          <t>811929</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>668854</t>
+          <t>670252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>728183</t>
+          <t>726230</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1454124</t>
+          <t>1452546</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1524795</t>
+          <t>1526423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110641</t>
+          <t>111596</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154283</t>
+          <t>155899</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>182234</t>
+          <t>183048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>227707</t>
+          <t>229099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>306722</t>
+          <t>305097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>371239</t>
+          <t>368526</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517379</t>
+          <t>515763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>561021</t>
+          <t>560066</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441281</t>
+          <t>439889</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>486754</t>
+          <t>485940</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>969411</t>
+          <t>972124</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1033928</t>
+          <t>1035553</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>170691</t>
+          <t>170973</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>220441</t>
+          <t>217708</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>273669</t>
+          <t>278025</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>333019</t>
+          <t>335016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>461321</t>
+          <t>463418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>533936</t>
+          <t>537936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>705696</t>
+          <t>708429</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>755446</t>
+          <t>755164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>683780</t>
+          <t>681783</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>743130</t>
+          <t>738774</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1408999</t>
+          <t>1404999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1481614</t>
+          <t>1479517</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>542936</t>
+          <t>539752</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>627470</t>
+          <t>628141</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>873730</t>
+          <t>872523</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>977973</t>
+          <t>974556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1443179</t>
+          <t>1440326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1577379</t>
+          <t>1578494</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2603359</t>
+          <t>2602688</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2687893</t>
+          <t>2691077</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2336996</t>
+          <t>2340413</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2441239</t>
+          <t>2442446</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4968419</t>
+          <t>4967304</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5102619</t>
+          <t>5105472</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,0%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>176615</t>
+          <t>175097</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>223530</t>
+          <t>225716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>186372</t>
+          <t>186229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>236414</t>
+          <t>234470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>373794</t>
+          <t>375864</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>443614</t>
+          <t>446157</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>476842</t>
+          <t>474656</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>523757</t>
+          <t>525275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>455618</t>
+          <t>457562</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>505660</t>
+          <t>505803</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>948790</t>
+          <t>946247</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1018610</t>
+          <t>1016540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,01%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>328435</t>
+          <t>327452</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>390370</t>
+          <t>390675</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>331956</t>
+          <t>330629</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>394949</t>
+          <t>393212</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>682816</t>
+          <t>677763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>770833</t>
+          <t>770871</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>623176</t>
+          <t>622871</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>685111</t>
+          <t>686094</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>628834</t>
+          <t>630571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>691827</t>
+          <t>693154</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1266495</t>
+          <t>1266457</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1354512</t>
+          <t>1359565</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,73%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>240680</t>
+          <t>240957</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>295341</t>
+          <t>295478</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>259068</t>
+          <t>255960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>311437</t>
+          <t>313652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>510449</t>
+          <t>517281</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>588563</t>
+          <t>591824</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>458373</t>
+          <t>458236</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513034</t>
+          <t>512757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>463569</t>
+          <t>461354</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>515938</t>
+          <t>519046</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>940157</t>
+          <t>936896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1018271</t>
+          <t>1011439</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,16%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>194837</t>
+          <t>195797</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>246274</t>
+          <t>245562</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>232744</t>
+          <t>232821</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>288747</t>
+          <t>289687</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>442873</t>
+          <t>441226</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>520004</t>
+          <t>520429</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>695240</t>
+          <t>695952</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>746677</t>
+          <t>745717</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>763154</t>
+          <t>762214</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>819157</t>
+          <t>819080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1473411</t>
+          <t>1472986</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1550542</t>
+          <t>1552189</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,87%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>988394</t>
+          <t>989070</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1099963</t>
+          <t>1096750</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1059267</t>
+          <t>1061488</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1179250</t>
+          <t>1178397</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2087027</t>
+          <t>2084308</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2239782</t>
+          <t>2246181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2309182</t>
+          <t>2312395</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2420751</t>
+          <t>2420075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2363472</t>
+          <t>2364325</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2483455</t>
+          <t>2481234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4712085</t>
+          <t>4705686</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4864840</t>
+          <t>4867559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,02%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>206811</t>
+          <t>206014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>258133</t>
+          <t>255200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>206678</t>
+          <t>204797</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>255170</t>
+          <t>253518</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>429017</t>
+          <t>426902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>499943</t>
+          <t>494618</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>407198</t>
+          <t>410131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>458520</t>
+          <t>459317</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>409742</t>
+          <t>411394</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>458234</t>
+          <t>460115</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>830300</t>
+          <t>835625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>901226</t>
+          <t>903341</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>313925</t>
+          <t>312588</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>378984</t>
+          <t>377085</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>330549</t>
+          <t>335967</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>392066</t>
+          <t>396084</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>663199</t>
+          <t>668277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>750105</t>
+          <t>756450</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>635539</t>
+          <t>637438</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>700598</t>
+          <t>701935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>643085</t>
+          <t>639067</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>704602</t>
+          <t>699184</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1299568</t>
+          <t>1293223</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1386474</t>
+          <t>1381396</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,4%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>290974</t>
+          <t>291104</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>348060</t>
+          <t>347067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>336772</t>
+          <t>336568</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>393484</t>
+          <t>393440</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>643005</t>
+          <t>646278</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>729322</t>
+          <t>724896</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,1%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>406978</t>
+          <t>407971</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>464064</t>
+          <t>463934</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>390463</t>
+          <t>390507</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>447175</t>
+          <t>447379</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>809663</t>
+          <t>814089</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>895980</t>
+          <t>892707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>208081</t>
+          <t>204650</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>261068</t>
+          <t>257704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>270746</t>
+          <t>272052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>331726</t>
+          <t>333425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>492717</t>
+          <t>492426</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>569818</t>
+          <t>573071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>671322</t>
+          <t>674686</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>724309</t>
+          <t>727740</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>711057</t>
+          <t>709358</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>772037</t>
+          <t>770731</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1405355</t>
+          <t>1402102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1482456</t>
+          <t>1482747</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1069847</t>
+          <t>1072306</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1184093</t>
+          <t>1181665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1198004</t>
+          <t>1201964</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1315886</t>
+          <t>1319856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2314822</t>
+          <t>2305668</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2470344</t>
+          <t>2468465</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2183189</t>
+          <t>2185617</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2297435</t>
+          <t>2294976</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2210906</t>
+          <t>2206936</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2328788</t>
+          <t>2324828</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4423731</t>
+          <t>4425610</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4579253</t>
+          <t>4588407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>72479</t>
+          <t>88632</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58071</t>
+          <t>71696</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90163</t>
+          <t>106642</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>108418</t>
+          <t>123263</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84682</t>
+          <t>107490</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127233</t>
+          <t>140416</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>180896</t>
+          <t>211895</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155323</t>
+          <t>189366</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>206250</t>
+          <t>243158</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>544866</t>
+          <t>583748</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>527182</t>
+          <t>565738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>559274</t>
+          <t>600684</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>604672</t>
+          <t>597854</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>585857</t>
+          <t>580701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>628408</t>
+          <t>613627</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1149538</t>
+          <t>1181601</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1124184</t>
+          <t>1150338</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1175111</t>
+          <t>1204130</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>617345</t>
+          <t>672380</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>617345</t>
+          <t>672380</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>617345</t>
+          <t>672380</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>713090</t>
+          <t>721117</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>713090</t>
+          <t>721117</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>713090</t>
+          <t>721117</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1330434</t>
+          <t>1393496</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1330434</t>
+          <t>1393496</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1330434</t>
+          <t>1393496</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>110600</t>
+          <t>137277</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49142</t>
+          <t>112657</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146534</t>
+          <t>164423</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>133377</t>
+          <t>154389</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>115969</t>
+          <t>134437</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>153218</t>
+          <t>178459</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>243978</t>
+          <t>291665</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163393</t>
+          <t>262785</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>289754</t>
+          <t>323269</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1070808</t>
+          <t>899064</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1034874</t>
+          <t>871918</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1132266</t>
+          <t>923684</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>817430</t>
+          <t>908640</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>797589</t>
+          <t>884570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>834838</t>
+          <t>928592</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1888237</t>
+          <t>1807705</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1842461</t>
+          <t>1776101</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1968822</t>
+          <t>1836585</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>87,48%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1181408</t>
+          <t>1036341</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1181408</t>
+          <t>1036341</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1181408</t>
+          <t>1036341</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>950807</t>
+          <t>1063029</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>950807</t>
+          <t>1063029</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>950807</t>
+          <t>1063029</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2132215</t>
+          <t>2099370</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2132215</t>
+          <t>2099370</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2132215</t>
+          <t>2099370</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>94741</t>
+          <t>110665</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76375</t>
+          <t>88777</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117753</t>
+          <t>135066</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>117366</t>
+          <t>139805</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58466</t>
+          <t>120149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>161549</t>
+          <t>159279</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>212107</t>
+          <t>250470</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125974</t>
+          <t>221204</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256120</t>
+          <t>283019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>605185</t>
+          <t>683559</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>582173</t>
+          <t>659158</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623551</t>
+          <t>705447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>778497</t>
+          <t>665613</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>734314</t>
+          <t>646139</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>837397</t>
+          <t>685269</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1383682</t>
+          <t>1349172</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1339669</t>
+          <t>1316623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1469815</t>
+          <t>1378438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>86,17%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>699926</t>
+          <t>794224</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>699926</t>
+          <t>794224</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>699926</t>
+          <t>794224</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>895863</t>
+          <t>805418</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>895863</t>
+          <t>805418</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>895863</t>
+          <t>805418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1595789</t>
+          <t>1599642</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1595789</t>
+          <t>1599642</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1595789</t>
+          <t>1599642</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>136578</t>
+          <t>162165</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111344</t>
+          <t>136833</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>158649</t>
+          <t>187657</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>248407</t>
+          <t>206123</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182900</t>
+          <t>183956</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>425367</t>
+          <t>230857</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>384985</t>
+          <t>368289</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>316729</t>
+          <t>334558</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>589047</t>
+          <t>404231</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>780647</t>
+          <t>816174</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>758576</t>
+          <t>790682</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>805881</t>
+          <t>841506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>835554</t>
+          <t>901730</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>658594</t>
+          <t>876996</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>901061</t>
+          <t>923897</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1616202</t>
+          <t>1717903</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1412140</t>
+          <t>1681961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1684458</t>
+          <t>1751634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>917225</t>
+          <t>978339</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>917225</t>
+          <t>978339</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>917225</t>
+          <t>978339</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1083961</t>
+          <t>1107853</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1083961</t>
+          <t>1107853</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1083961</t>
+          <t>1107853</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2001187</t>
+          <t>2086192</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2001187</t>
+          <t>2086192</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2001187</t>
+          <t>2086192</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>414398</t>
+          <t>498739</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>317457</t>
+          <t>452722</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>466090</t>
+          <t>545741</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>607568</t>
+          <t>623580</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>504971</t>
+          <t>581647</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>788405</t>
+          <t>665420</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1021966</t>
+          <t>1122320</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>894116</t>
+          <t>1057634</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1219741</t>
+          <t>1186356</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3001505</t>
+          <t>2982545</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2949813</t>
+          <t>2935543</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3098446</t>
+          <t>3028562</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3036154</t>
+          <t>3073836</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2855317</t>
+          <t>3031996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3138751</t>
+          <t>3115769</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6037659</t>
+          <t>6056381</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5839884</t>
+          <t>5992345</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6165509</t>
+          <t>6121067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3415903</t>
+          <t>3481284</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3415903</t>
+          <t>3481284</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3415903</t>
+          <t>3481284</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3643722</t>
+          <t>3697416</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3643722</t>
+          <t>3697416</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3643722</t>
+          <t>3697416</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7059625</t>
+          <t>7178701</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7059625</t>
+          <t>7178701</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7059625</t>
+          <t>7178701</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
